--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B52679FC-B784-4589-B590-BD14CDDAF4C5}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C650A8AB-C103-4C56-8487-AEA7D9908CDF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="8" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
@@ -730,10 +730,10 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -795,13 +795,13 @@
         <v>S2</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C650A8AB-C103-4C56-8487-AEA7D9908CDF}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1267FFAC-C233-460D-9ACB-7991AC09EBCA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="8" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
@@ -730,7 +730,7 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1267FFAC-C233-460D-9ACB-7991AC09EBCA}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF75254-8B48-4E78-B32B-6AD841145544}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="10" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
@@ -733,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -801,7 +801,7 @@
         <v>100</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D23C0BA8-594D-4BFA-8AF4-6F394CA3A874}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E56A4109-2E89-4416-A3FD-5F5D00765381}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="4" activeTab="11" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="2" activeTab="11" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
@@ -682,13 +682,13 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -696,13 +696,13 @@
         <v>S2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -790,7 +790,7 @@
         <v>400</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -804,7 +804,7 @@
         <v>400</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1037,7 +1037,7 @@
         <v>168</v>
       </c>
       <c r="J3">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="K3">
         <v>50</v>
@@ -1295,7 +1295,7 @@
         <v>35</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -1306,7 +1306,7 @@
         <v>36</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1340,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1351,7 +1351,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1362,7 +1362,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E56A4109-2E89-4416-A3FD-5F5D00765381}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E6C308B-BF27-4FEA-90A5-1953FAE14838}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="2" activeTab="11" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="2" activeTab="9" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
@@ -733,10 +733,10 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>S1</v>
       </c>
       <c r="B2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="C2">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="D2">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -798,13 +798,13 @@
         <v>S2</v>
       </c>
       <c r="B3">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="C3">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="D3">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1124,7 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>16</v>
       </c>
       <c r="E3">
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1295,7 +1295,7 @@
         <v>35</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -1306,7 +1306,7 @@
         <v>36</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>3</v>

--- a/data/Inputs.xlsx
+++ b/data/Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3dd903d477a9e4d/02_ME/ME54015/OWF_Vessel-Fleet-Optimization/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E6C308B-BF27-4FEA-90A5-1953FAE14838}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="13_ncr:1_{4E655DA3-6644-44D5-B8A3-390376DF86AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03B2820E-D429-4348-959C-D2337DFE70F1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="2" activeTab="9" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="853" firstSheet="2" activeTab="6" xr2:uid="{5CDB4E5C-34BF-4466-8F20-CB91BE55E2BE}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="5" r:id="rId1"/>
